--- a/Employee_Reports_wi48/Sajith Dulanjana Kumara Rathnayaka Mudiyanselage Q0626.xlsx
+++ b/Employee_Reports_wi48/Sajith Dulanjana Kumara Rathnayaka Mudiyanselage Q0626.xlsx
@@ -560,11 +560,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -609,11 +609,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -805,11 +805,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -854,11 +854,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -952,11 +952,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1050,11 +1050,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1099,11 +1099,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1136,11 +1136,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1185,11 +1185,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1235,11 +1235,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1284,11 +1284,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1333,11 +1333,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1382,11 +1382,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7933</v>
+        <v>7930</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7981</v>
+        <v>7978</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7981</v>
+        <v>7978</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7981</v>
+        <v>7978</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7981</v>
+        <v>7978</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7979</v>
+        <v>7976</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
